--- a/countries/ch/2026-2029.xlsx
+++ b/countries/ch/2026-2029.xlsx
@@ -20408,13 +20408,13 @@
         </is>
       </c>
       <c r="N135" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="O135" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="R135" t="n">
-        <v>1.232265643612346</v>
+        <v>1.243367135897142</v>
       </c>
       <c r="S135" t="inlineStr">
         <is>
@@ -25731,13 +25731,13 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="O171" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="R171" t="n">
-        <v>1.476498473877856</v>
+        <v>1.532005935301835</v>
       </c>
       <c r="S171" t="inlineStr">
         <is>
@@ -30329,13 +30329,13 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="O202" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="R202" t="n">
-        <v>1.820644734706529</v>
+        <v>1.831746226991325</v>
       </c>
       <c r="S202" t="inlineStr">
         <is>
@@ -30909,13 +30909,13 @@
         </is>
       </c>
       <c r="N206" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O206" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="R206" t="n">
-        <v>0.07771044599357135</v>
+        <v>0.08881193827836725</v>
       </c>
       <c r="S206" t="inlineStr">
         <is>
@@ -31054,13 +31054,13 @@
         </is>
       </c>
       <c r="N207" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O207" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R207" t="n">
-        <v>0.06660895370877544</v>
+        <v>0.07771044599357135</v>
       </c>
       <c r="S207" t="inlineStr">
         <is>
@@ -31924,13 +31924,13 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="O213" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R213" t="n">
-        <v>0.2442328302655099</v>
+        <v>0.2553343225503059</v>
       </c>
       <c r="S213" t="inlineStr">
         <is>
@@ -32794,13 +32794,13 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="O219" t="n">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="R219" t="n">
-        <v>2.697662625205405</v>
+        <v>2.964098440040507</v>
       </c>
       <c r="S219" t="inlineStr">
         <is>
@@ -33157,6 +33157,1166 @@
         </is>
       </c>
       <c r="BC221" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I222" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J222" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L222" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M222" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N222" t="n">
+        <v>113</v>
+      </c>
+      <c r="O222" t="n">
+        <v>113</v>
+      </c>
+      <c r="R222" t="n">
+        <v>1.254468628181937</v>
+      </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO222" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP222" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR222" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS222" t="inlineStr"/>
+      <c r="AT222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU222" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV222" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW222" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX222" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY222" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA222" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB222" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC222" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I223" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J223" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L223" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M223" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N223" t="n">
+        <v>10</v>
+      </c>
+      <c r="O223" t="n">
+        <v>10</v>
+      </c>
+      <c r="R223" t="n">
+        <v>0.1110149228479591</v>
+      </c>
+      <c r="S223" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO223" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP223" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR223" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS223" t="inlineStr"/>
+      <c r="AT223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU223" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV223" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW223" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX223" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY223" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA223" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB223" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC223" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I224" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J224" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L224" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M224" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N224" t="n">
+        <v>8</v>
+      </c>
+      <c r="O224" t="n">
+        <v>8</v>
+      </c>
+      <c r="R224" t="n">
+        <v>0.08881193827836725</v>
+      </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO224" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP224" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR224" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS224" t="inlineStr"/>
+      <c r="AT224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU224" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV224" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW224" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX224" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY224" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA224" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB224" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC224" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H225" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I225" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N225" t="n">
+        <v>125</v>
+      </c>
+      <c r="O225" t="n">
+        <v>125</v>
+      </c>
+      <c r="R225" t="n">
+        <v>1.387686535599488</v>
+      </c>
+      <c r="S225" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO225" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP225" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR225" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr"/>
+      <c r="AT225" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU225" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV225" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW225" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX225" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY225" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA225" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB225" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC225" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>D092</t>
+        </is>
+      </c>
+      <c r="I226" t="inlineStr">
+        <is>
+          <t>Campylobacteriosis</t>
+        </is>
+      </c>
+      <c r="J226" t="inlineStr">
+        <is>
+          <t>弯曲杆菌病</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L226" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N226" t="n">
+        <v>1392</v>
+      </c>
+      <c r="O226" t="n">
+        <v>1392</v>
+      </c>
+      <c r="R226" t="n">
+        <v>15.4532772604359</v>
+      </c>
+      <c r="S226" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO226" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP226" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR226" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS226" t="inlineStr"/>
+      <c r="AT226" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU226" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV226" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW226" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX226" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY226" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA226" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB226" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC226" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I227" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N227" t="n">
+        <v>27</v>
+      </c>
+      <c r="O227" t="n">
+        <v>27</v>
+      </c>
+      <c r="R227" t="n">
+        <v>0.2997402916894895</v>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO227" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP227" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR227" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS227" t="inlineStr"/>
+      <c r="AT227" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU227" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV227" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW227" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX227" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY227" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA227" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB227" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC227" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H228" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I228" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J228" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L228" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M228" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N228" t="n">
+        <v>555</v>
+      </c>
+      <c r="O228" t="n">
+        <v>555</v>
+      </c>
+      <c r="R228" t="n">
+        <v>6.161328218061729</v>
+      </c>
+      <c r="S228" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO228" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP228" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR228" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS228" t="inlineStr"/>
+      <c r="AT228" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU228" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV228" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW228" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX228" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY228" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA228" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB228" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC228" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N229" t="n">
+        <v>261</v>
+      </c>
+      <c r="O229" t="n">
+        <v>261</v>
+      </c>
+      <c r="R229" t="n">
+        <v>2.897489486331732</v>
+      </c>
+      <c r="S229" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO229" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP229" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR229" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS229" t="inlineStr"/>
+      <c r="AT229" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU229" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV229" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW229" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX229" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY229" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA229" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB229" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC229" t="inlineStr">
         <is>
           <t>rest_api</t>
         </is>
@@ -33195,7 +34355,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
@@ -33278,7 +34438,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>215</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10">
@@ -33288,7 +34448,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>220</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11">
@@ -33340,7 +34500,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>54706</v>
+        <v>57231</v>
       </c>
     </row>
     <row r="16">

--- a/countries/ch/2026-2029.xlsx
+++ b/countries/ch/2026-2029.xlsx
@@ -14354,13 +14354,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="O94" t="n">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="R94" t="n">
-        <v>2.897489486331732</v>
+        <v>2.886387994046936</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -19973,13 +19973,13 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="O132" t="n">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="R132" t="n">
-        <v>4.351784975639996</v>
+        <v>4.3406834833552</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
@@ -25296,13 +25296,13 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="O168" t="n">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="R168" t="n">
-        <v>9.691602764626827</v>
+        <v>9.636095303202847</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -26414,13 +26414,13 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="O175" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="R175" t="n">
-        <v>0.7437999830813258</v>
+        <v>0.721596998511734</v>
       </c>
       <c r="S175" t="inlineStr">
         <is>
@@ -29894,13 +29894,13 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>2183</v>
+        <v>2173</v>
       </c>
       <c r="O199" t="n">
-        <v>2183</v>
+        <v>2173</v>
       </c>
       <c r="R199" t="n">
-        <v>24.23455765770947</v>
+        <v>24.12354273486151</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
@@ -30474,13 +30474,13 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="O203" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="R203" t="n">
-        <v>0.2331313379807141</v>
+        <v>0.2442328302655099</v>
       </c>
       <c r="S203" t="inlineStr">
         <is>
@@ -30619,13 +30619,13 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O204" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R204" t="n">
-        <v>1.365483551029897</v>
+        <v>1.398788027884284</v>
       </c>
       <c r="S204" t="inlineStr">
         <is>
@@ -32359,13 +32359,13 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>1746</v>
+        <v>1737</v>
       </c>
       <c r="O216" t="n">
-        <v>1746</v>
+        <v>1737</v>
       </c>
       <c r="R216" t="n">
-        <v>19.38320552925365</v>
+        <v>19.28329209869049</v>
       </c>
       <c r="S216" t="inlineStr">
         <is>
@@ -32939,13 +32939,13 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="O220" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="R220" t="n">
-        <v>0.1998268611263263</v>
+        <v>0.2553343225503059</v>
       </c>
       <c r="S220" t="inlineStr">
         <is>
@@ -33084,13 +33084,13 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O221" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R221" t="n">
-        <v>1.121250720764387</v>
+        <v>1.143453705333978</v>
       </c>
       <c r="S221" t="inlineStr">
         <is>
@@ -33664,13 +33664,13 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="O225" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="R225" t="n">
-        <v>1.387686535599488</v>
+        <v>1.432092504738672</v>
       </c>
       <c r="S225" t="inlineStr">
         <is>
@@ -34070,17 +34070,17 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>D114</t>
+          <t>D109</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Salmonellosis</t>
+          <t>Lyme disease</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>沙门氏菌病</t>
+          <t>莱姆病</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -34099,13 +34099,13 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>555</v>
+        <v>1129</v>
       </c>
       <c r="O228" t="n">
-        <v>555</v>
+        <v>1129</v>
       </c>
       <c r="R228" t="n">
-        <v>6.161328218061729</v>
+        <v>12.53358478953458</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
@@ -34215,17 +34215,17 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>D115</t>
+          <t>D114</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>Shiga toxin-producing Escherichia coli infection</t>
+          <t>Salmonellosis</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>产志贺毒素大肠杆菌感染</t>
+          <t>沙门氏菌病</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -34244,13 +34244,13 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>261</v>
+        <v>555</v>
       </c>
       <c r="O229" t="n">
-        <v>261</v>
+        <v>555</v>
       </c>
       <c r="R229" t="n">
-        <v>2.897489486331732</v>
+        <v>6.161328218061729</v>
       </c>
       <c r="S229" t="inlineStr">
         <is>
@@ -34317,6 +34317,441 @@
         </is>
       </c>
       <c r="BC229" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H230" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I230" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J230" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L230" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M230" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N230" t="n">
+        <v>261</v>
+      </c>
+      <c r="O230" t="n">
+        <v>261</v>
+      </c>
+      <c r="R230" t="n">
+        <v>2.897489486331732</v>
+      </c>
+      <c r="S230" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO230" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP230" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR230" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS230" t="inlineStr"/>
+      <c r="AT230" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU230" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV230" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW230" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX230" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY230" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA230" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB230" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC230" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H231" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I231" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J231" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L231" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N231" t="n">
+        <v>8</v>
+      </c>
+      <c r="O231" t="n">
+        <v>8</v>
+      </c>
+      <c r="R231" t="n">
+        <v>0.08881193827836725</v>
+      </c>
+      <c r="S231" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO231" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP231" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR231" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS231" t="inlineStr"/>
+      <c r="AT231" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU231" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV231" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW231" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX231" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY231" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA231" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB231" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC231" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J232" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L232" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M232" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N232" t="n">
+        <v>25</v>
+      </c>
+      <c r="O232" t="n">
+        <v>25</v>
+      </c>
+      <c r="R232" t="n">
+        <v>0.2775373071198977</v>
+      </c>
+      <c r="S232" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO232" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP232" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR232" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS232" t="inlineStr"/>
+      <c r="AT232" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU232" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV232" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW232" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX232" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY232" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA232" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB232" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC232" t="inlineStr">
         <is>
           <t>rest_api</t>
         </is>
@@ -34438,7 +34873,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>223</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10">
@@ -34448,7 +34883,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
@@ -34500,7 +34935,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>57231</v>
+        <v>58380</v>
       </c>
     </row>
     <row r="16">

--- a/countries/ch/2026-2029.xlsx
+++ b/countries/ch/2026-2029.xlsx
@@ -4626,7 +4626,7 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK28" t="inlineStr">
@@ -9973,7 +9973,7 @@
       </c>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -15320,7 +15320,7 @@
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -20939,7 +20939,7 @@
       </c>
       <c r="AJ138" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK138" t="inlineStr">
@@ -26262,7 +26262,7 @@
       </c>
       <c r="AJ174" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.30.1</t>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
         </is>
       </c>
       <c r="AK174" t="inlineStr">

--- a/countries/ch/2026-2029.xlsx
+++ b/countries/ch/2026-2029.xlsx
@@ -33229,13 +33229,13 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="O222" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="R222" t="n">
-        <v>1.254468628181937</v>
+        <v>1.265570120466733</v>
       </c>
       <c r="S222" t="inlineStr">
         <is>
@@ -34935,7 +34935,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>58380</v>
+        <v>58381</v>
       </c>
     </row>
     <row r="16">

--- a/countries/ch/2026-2029.xlsx
+++ b/countries/ch/2026-2029.xlsx
@@ -918,6 +918,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1063,6 +1068,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1208,6 +1218,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1353,6 +1368,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1933,6 +1953,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2078,6 +2103,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2658,6 +2688,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2803,6 +2838,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3093,6 +3133,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3673,6 +3718,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3963,6 +4013,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4108,6 +4163,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4253,6 +4313,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4791,6 +4856,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6265,6 +6335,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6410,6 +6485,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6555,6 +6635,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6700,6 +6785,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7280,6 +7370,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7425,6 +7520,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8005,6 +8105,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8150,6 +8255,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8440,6 +8550,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9020,6 +9135,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9310,6 +9430,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9455,6 +9580,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9600,6 +9730,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10138,6 +10273,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11612,6 +11752,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11744,17 +11889,22 @@
         </is>
       </c>
       <c r="N76" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="O76" t="n">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="R76" t="n">
-        <v>1.298874597321121</v>
+        <v>1.243367135897142</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO76" t="inlineStr">
@@ -11902,6 +12052,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12047,6 +12202,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12324,13 +12484,13 @@
         </is>
       </c>
       <c r="N80" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O80" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="R80" t="n">
-        <v>0.1332179074175509</v>
+        <v>0.1443193997023468</v>
       </c>
       <c r="S80" t="inlineStr">
         <is>
@@ -12614,17 +12774,22 @@
         </is>
       </c>
       <c r="N82" t="n">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O82" t="n">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="R82" t="n">
-        <v>6.028110310644178</v>
+        <v>6.039211802928973</v>
       </c>
       <c r="S82" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
@@ -12759,17 +12924,22 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="O83" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="R83" t="n">
-        <v>1.176758182188366</v>
+        <v>1.210062659042754</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
@@ -13352,6 +13522,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13484,17 +13659,22 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="O88" t="n">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="R88" t="n">
-        <v>13.54382058745101</v>
+        <v>13.5660235720206</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
@@ -13787,6 +13967,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14354,17 +14539,22 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O94" t="n">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="R94" t="n">
-        <v>2.886387994046936</v>
+        <v>2.908590978616528</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO94" t="inlineStr">
@@ -14657,6 +14847,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14802,6 +14997,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14947,6 +15147,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15485,6 +15690,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17231,6 +17441,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17363,17 +17578,22 @@
         </is>
       </c>
       <c r="N114" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="O114" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="R114" t="n">
-        <v>1.076844751625203</v>
+        <v>1.021337290201223</v>
       </c>
       <c r="S114" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO114" t="inlineStr">
@@ -17521,6 +17741,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17666,6 +17891,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17943,13 +18173,13 @@
         </is>
       </c>
       <c r="N118" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O118" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="R118" t="n">
-        <v>0.1665223842719386</v>
+        <v>0.1776238765567345</v>
       </c>
       <c r="S118" t="inlineStr">
         <is>
@@ -18233,17 +18463,22 @@
         </is>
       </c>
       <c r="N120" t="n">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="O120" t="n">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="R120" t="n">
-        <v>5.683964049815504</v>
+        <v>5.672862557530708</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO120" t="inlineStr">
@@ -18391,6 +18626,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18813,13 +19053,13 @@
         </is>
       </c>
       <c r="N124" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="O124" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="R124" t="n">
-        <v>0.09991343056316315</v>
+        <v>0.1110149228479591</v>
       </c>
       <c r="S124" t="inlineStr">
         <is>
@@ -18971,6 +19211,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19116,6 +19361,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19406,6 +19656,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19683,13 +19938,13 @@
         </is>
       </c>
       <c r="N130" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="O130" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="R130" t="n">
-        <v>0.2331313379807141</v>
+        <v>0.2553343225503059</v>
       </c>
       <c r="S130" t="inlineStr">
         <is>
@@ -19973,17 +20228,22 @@
         </is>
       </c>
       <c r="N132" t="n">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="O132" t="n">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="R132" t="n">
-        <v>4.3406834833552</v>
+        <v>4.373987960209587</v>
       </c>
       <c r="S132" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO132" t="inlineStr">
@@ -20276,6 +20536,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20421,6 +20686,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20566,6 +20836,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21104,6 +21379,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22554,6 +22834,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22686,17 +22971,22 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="O150" t="n">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="R150" t="n">
-        <v>1.243367135897142</v>
+        <v>1.16565668990357</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO150" t="inlineStr">
@@ -22844,6 +23134,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22989,6 +23284,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23411,13 +23711,13 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="O155" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="R155" t="n">
-        <v>0.5328716296702035</v>
+        <v>0.5439731219549995</v>
       </c>
       <c r="S155" t="inlineStr">
         <is>
@@ -23556,17 +23856,22 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="O156" t="n">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="R156" t="n">
-        <v>5.595152111537137</v>
+        <v>5.584050619252341</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO156" t="inlineStr">
@@ -23701,17 +24006,22 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="O157" t="n">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="R157" t="n">
-        <v>0.9325253519228562</v>
+        <v>1.010235797916428</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO157" t="inlineStr">
@@ -24294,6 +24604,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24439,6 +24754,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24729,6 +25049,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25296,17 +25621,22 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>868</v>
+        <v>876</v>
       </c>
       <c r="O168" t="n">
-        <v>868</v>
+        <v>876</v>
       </c>
       <c r="R168" t="n">
-        <v>9.636095303202847</v>
+        <v>9.724907241481215</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO168" t="inlineStr">
@@ -25599,6 +25929,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25744,6 +26079,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25889,6 +26229,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26427,6 +26772,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27877,6 +28227,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27980,17 +28335,17 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>D011</t>
+          <t>D008</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Hepatitis E</t>
+          <t>Hepatitis B</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>戊型肝炎</t>
+          <t>乙型肝炎</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
@@ -28009,17 +28364,22 @@
         </is>
       </c>
       <c r="N186" t="n">
-        <v>12</v>
+        <v>119</v>
       </c>
       <c r="O186" t="n">
-        <v>12</v>
+        <v>119</v>
       </c>
       <c r="R186" t="n">
-        <v>0.1332179074175509</v>
+        <v>1.321077581890713</v>
       </c>
       <c r="S186" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO186" t="inlineStr">
@@ -28125,17 +28485,17 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>D017</t>
+          <t>D009</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Measles</t>
+          <t>Hepatitis C</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>麻疹</t>
+          <t>丙型肝炎</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
@@ -28154,17 +28514,22 @@
         </is>
       </c>
       <c r="N187" t="n">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="O187" t="n">
-        <v>1</v>
+        <v>98</v>
       </c>
       <c r="R187" t="n">
-        <v>0.01110149228479591</v>
+        <v>1.087946243909999</v>
       </c>
       <c r="S187" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO187" t="inlineStr">
@@ -28270,17 +28635,17 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>D021</t>
+          <t>D011</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Dengue</t>
+          <t>Hepatitis E</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>登革热</t>
+          <t>戊型肝炎</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -28299,17 +28664,22 @@
         </is>
       </c>
       <c r="N188" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="O188" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="R188" t="n">
-        <v>0.1110149228479591</v>
+        <v>0.1332179074175509</v>
       </c>
       <c r="S188" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO188" t="inlineStr">
@@ -28415,22 +28785,22 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>D025</t>
+          <t>D017</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Tuberculosis</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>肺结核</t>
+          <t>麻疹</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -28444,13 +28814,13 @@
         </is>
       </c>
       <c r="N189" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="O189" t="n">
-        <v>47</v>
+        <v>1</v>
       </c>
       <c r="R189" t="n">
-        <v>0.5217701373854076</v>
+        <v>0.01110149228479591</v>
       </c>
       <c r="S189" t="inlineStr">
         <is>
@@ -28560,22 +28930,22 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>D037</t>
+          <t>D021</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>Malaria</t>
+          <t>Dengue</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>疟疾</t>
+          <t>登革热</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
@@ -28589,13 +28959,13 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="O190" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="R190" t="n">
-        <v>0.2109283534111222</v>
+        <v>0.1110149228479591</v>
       </c>
       <c r="S190" t="inlineStr">
         <is>
@@ -28705,22 +29075,22 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>D038</t>
+          <t>D025</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Tuberculosis</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>流行性感冒</t>
+          <t>肺结核</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -28734,13 +29104,13 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="O191" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="R191" t="n">
-        <v>0.4107552145374486</v>
+        <v>0.5217701373854076</v>
       </c>
       <c r="S191" t="inlineStr">
         <is>
@@ -28850,22 +29220,22 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>D052</t>
+          <t>D033</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>Chikungunya</t>
+          <t>Gonorrhea</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>基孔肯雅热</t>
+          <t>淋病</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -28879,17 +29249,22 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>2</v>
+        <v>555</v>
       </c>
       <c r="O192" t="n">
-        <v>2</v>
+        <v>555</v>
       </c>
       <c r="R192" t="n">
-        <v>0.02220298456959181</v>
+        <v>6.161328218061729</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO192" t="inlineStr">
@@ -28995,17 +29370,17 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>D092</t>
+          <t>D034</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>Campylobacteriosis</t>
+          <t>Syphilis</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>弯曲杆菌病</t>
+          <t>梅毒</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
@@ -29024,17 +29399,22 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>1096</v>
+        <v>103</v>
       </c>
       <c r="O193" t="n">
-        <v>1096</v>
+        <v>103</v>
       </c>
       <c r="R193" t="n">
-        <v>12.16723554413631</v>
+        <v>1.143453705333978</v>
       </c>
       <c r="S193" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO193" t="inlineStr">
@@ -29140,22 +29520,22 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>D100</t>
+          <t>D037</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>Haemophilus influenzae</t>
+          <t>Malaria</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>流感嗜血杆菌</t>
+          <t>疟疾</t>
         </is>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
@@ -29169,13 +29549,13 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="O194" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="R194" t="n">
-        <v>0.1554208919871427</v>
+        <v>0.1998268611263263</v>
       </c>
       <c r="S194" t="inlineStr">
         <is>
@@ -29285,22 +29665,22 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>D105</t>
+          <t>D038</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>Shigellosis</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>志贺菌病</t>
+          <t>流行性感冒</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -29314,13 +29694,13 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="O195" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="R195" t="n">
-        <v>0.2553343225503059</v>
+        <v>0.4107552145374486</v>
       </c>
       <c r="S195" t="inlineStr">
         <is>
@@ -29430,22 +29810,22 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>D106</t>
+          <t>D052</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>Invasive pneumococcal disease</t>
+          <t>Chikungunya</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>侵袭性肺炎球菌病</t>
+          <t>基孔肯雅热</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -29459,13 +29839,13 @@
         </is>
       </c>
       <c r="N196" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="O196" t="n">
-        <v>46</v>
+        <v>2</v>
       </c>
       <c r="R196" t="n">
-        <v>0.5106686451006117</v>
+        <v>0.02220298456959181</v>
       </c>
       <c r="S196" t="inlineStr">
         <is>
@@ -29575,17 +29955,17 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>D107</t>
+          <t>D092</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Legionellosis</t>
+          <t>Campylobacteriosis</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>军团菌病</t>
+          <t>弯曲杆菌病</t>
         </is>
       </c>
       <c r="K197" t="inlineStr">
@@ -29604,17 +29984,22 @@
         </is>
       </c>
       <c r="N197" t="n">
-        <v>38</v>
+        <v>1096</v>
       </c>
       <c r="O197" t="n">
-        <v>38</v>
+        <v>1096</v>
       </c>
       <c r="R197" t="n">
-        <v>0.4218567068222445</v>
+        <v>12.16723554413631</v>
       </c>
       <c r="S197" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO197" t="inlineStr">
@@ -29720,17 +30105,17 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>D108</t>
+          <t>D094</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>Listeriosis</t>
+          <t>Chlamydia trachomatis infection</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>李斯特菌病</t>
+          <t>沙眼衣原体感染</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
@@ -29749,17 +30134,22 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>4</v>
+        <v>1172</v>
       </c>
       <c r="O198" t="n">
-        <v>4</v>
+        <v>1172</v>
       </c>
       <c r="R198" t="n">
-        <v>0.04440596913918363</v>
+        <v>13.0109489577808</v>
       </c>
       <c r="S198" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO198" t="inlineStr">
@@ -29865,17 +30255,17 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>D109</t>
+          <t>D100</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>Lyme disease</t>
+          <t>Haemophilus influenzae</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>莱姆病</t>
+          <t>流感嗜血杆菌</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
@@ -29894,13 +30284,13 @@
         </is>
       </c>
       <c r="N199" t="n">
-        <v>2173</v>
+        <v>15</v>
       </c>
       <c r="O199" t="n">
-        <v>2173</v>
+        <v>15</v>
       </c>
       <c r="R199" t="n">
-        <v>24.12354273486151</v>
+        <v>0.1665223842719386</v>
       </c>
       <c r="S199" t="inlineStr">
         <is>
@@ -30010,17 +30400,17 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>D113</t>
+          <t>D105</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>Q fever</t>
+          <t>Shigellosis</t>
         </is>
       </c>
       <c r="J200" t="inlineStr">
         <is>
-          <t>Q热</t>
+          <t>志贺菌病</t>
         </is>
       </c>
       <c r="K200" t="inlineStr">
@@ -30039,17 +30429,22 @@
         </is>
       </c>
       <c r="N200" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="O200" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="R200" t="n">
-        <v>0.1554208919871427</v>
+        <v>0.2553343225503059</v>
       </c>
       <c r="S200" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO200" t="inlineStr">
@@ -30155,17 +30550,17 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>D114</t>
+          <t>D106</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Salmonellosis</t>
+          <t>Invasive pneumococcal disease</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>沙门氏菌病</t>
+          <t>侵袭性肺炎球菌病</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
@@ -30184,13 +30579,13 @@
         </is>
       </c>
       <c r="N201" t="n">
-        <v>170</v>
+        <v>46</v>
       </c>
       <c r="O201" t="n">
-        <v>170</v>
+        <v>46</v>
       </c>
       <c r="R201" t="n">
-        <v>1.887253688415304</v>
+        <v>0.5106686451006117</v>
       </c>
       <c r="S201" t="inlineStr">
         <is>
@@ -30300,17 +30695,17 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>D115</t>
+          <t>D107</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>Shiga toxin-producing Escherichia coli infection</t>
+          <t>Legionellosis</t>
         </is>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>产志贺毒素大肠杆菌感染</t>
+          <t>军团菌病</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
@@ -30329,13 +30724,13 @@
         </is>
       </c>
       <c r="N202" t="n">
-        <v>165</v>
+        <v>39</v>
       </c>
       <c r="O202" t="n">
-        <v>165</v>
+        <v>39</v>
       </c>
       <c r="R202" t="n">
-        <v>1.831746226991325</v>
+        <v>0.4329581991070403</v>
       </c>
       <c r="S202" t="inlineStr">
         <is>
@@ -30445,17 +30840,17 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>D123</t>
+          <t>D108</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>Tularemia</t>
+          <t>Listeriosis</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>土拉菌病</t>
+          <t>李斯特菌病</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
@@ -30474,13 +30869,13 @@
         </is>
       </c>
       <c r="N203" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="O203" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="R203" t="n">
-        <v>0.2442328302655099</v>
+        <v>0.04440596913918363</v>
       </c>
       <c r="S203" t="inlineStr">
         <is>
@@ -30590,22 +30985,22 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>D205</t>
+          <t>D109</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>Tick-borne encephalitis</t>
+          <t>Lyme disease</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>蜱传脑炎</t>
+          <t>莱姆病</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -30619,17 +31014,22 @@
         </is>
       </c>
       <c r="N204" t="n">
-        <v>126</v>
+        <v>2189</v>
       </c>
       <c r="O204" t="n">
-        <v>126</v>
+        <v>2189</v>
       </c>
       <c r="R204" t="n">
-        <v>1.398788027884284</v>
+        <v>24.30116661141824</v>
       </c>
       <c r="S204" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO204" t="inlineStr">
@@ -30735,42 +31135,42 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>D004</t>
+          <t>D113</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Q fever</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>新型冠状病毒感染</t>
+          <t>Q热</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N205" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="O205" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="R205" t="n">
-        <v>0.6327850602333667</v>
+        <v>0.1554208919871427</v>
       </c>
       <c r="S205" t="inlineStr">
         <is>
@@ -30880,46 +31280,51 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>D007</t>
+          <t>D114</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>Hepatitis A</t>
+          <t>Salmonellosis</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>甲型肝炎</t>
+          <t>沙门氏菌病</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N206" t="n">
-        <v>8</v>
+        <v>170</v>
       </c>
       <c r="O206" t="n">
-        <v>8</v>
+        <v>170</v>
       </c>
       <c r="R206" t="n">
-        <v>0.08881193827836725</v>
+        <v>1.887253688415304</v>
       </c>
       <c r="S206" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO206" t="inlineStr">
@@ -31025,46 +31430,51 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>D011</t>
+          <t>D115</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>Hepatitis E</t>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>戊型肝炎</t>
+          <t>产志贺毒素大肠杆菌感染</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N207" t="n">
-        <v>7</v>
+        <v>165</v>
       </c>
       <c r="O207" t="n">
-        <v>7</v>
+        <v>165</v>
       </c>
       <c r="R207" t="n">
-        <v>0.07771044599357135</v>
+        <v>1.831746226991325</v>
       </c>
       <c r="S207" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO207" t="inlineStr">
@@ -31170,46 +31580,51 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>D017</t>
+          <t>D123</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>Measles</t>
+          <t>Tularemia</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>麻疹</t>
+          <t>土拉菌病</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N208" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="O208" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="R208" t="n">
-        <v>0</v>
+        <v>0.2442328302655099</v>
       </c>
       <c r="S208" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO208" t="inlineStr">
@@ -31315,70 +31730,84 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>D037</t>
+          <t>D162</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Malaria</t>
+          <t>HIV infection</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>疟疾</t>
+          <t>人类免疫缺乏病毒感染</t>
         </is>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t>Parasitic</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N209" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="O209" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="R209" t="n">
-        <v>0.3441462608286731</v>
+        <v>0.3663492453982649</v>
       </c>
       <c r="S209" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U209" t="inlineStr">
+        <is>
+          <t>SER_CH_HIV_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR209" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS209" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ209" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS209" t="inlineStr">
+        <is>
+          <t>SER_CH_HIV_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT209" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU209" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV209" t="inlineStr">
@@ -31445,7 +31874,7 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -31460,17 +31889,17 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>D038</t>
+          <t>D162</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>HIV infection</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>流行性感冒</t>
+          <t>人类免疫缺乏病毒感染</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
@@ -31480,50 +31909,139 @@
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N210" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="O210" t="n">
-        <v>38</v>
-      </c>
-      <c r="R210" t="n">
-        <v>0.4218567068222445</v>
-      </c>
-      <c r="S210" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>33</v>
+      </c>
+      <c r="U210" t="inlineStr">
+        <is>
+          <t>SER_CH_HIV_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V210" t="inlineStr">
+        <is>
+          <t>SER_CH_HIV_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W210" t="inlineStr">
+        <is>
+          <t>SRC_CH_FOPH_IDD</t>
+        </is>
+      </c>
+      <c r="X210" t="inlineStr">
+        <is>
+          <t>Human Immunodeficiency Virus (HIV)</t>
+        </is>
+      </c>
+      <c r="Y210" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z210" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB210" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC210" t="inlineStr">
+        <is>
+          <t>country:CH:national</t>
+        </is>
+      </c>
+      <c r="AD210" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE210" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF210" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="AG210" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH210" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI210" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ210" t="inlineStr">
+        <is>
+          <t>globalid-disease-ontology:2026.09.26.1</t>
+        </is>
+      </c>
+      <c r="AK210" t="inlineStr">
+        <is>
+          <t>Source-reported HIV diagnoses at any reported stage.</t>
+        </is>
+      </c>
+      <c r="AM210" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN210" t="b">
+        <v>1</v>
       </c>
       <c r="AO210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP210" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR210" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS210" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ210" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS210" t="inlineStr">
+        <is>
+          <t>SER_CH_HIV_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU210" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV210" t="inlineStr">
@@ -31605,46 +32123,51 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>D092</t>
+          <t>D205</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>Campylobacteriosis</t>
+          <t>Tick-borne encephalitis</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>弯曲杆菌病</t>
+          <t>蜱传脑炎</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N211" t="n">
-        <v>1280</v>
+        <v>126</v>
       </c>
       <c r="O211" t="n">
-        <v>1280</v>
+        <v>126</v>
       </c>
       <c r="R211" t="n">
-        <v>14.20991012453876</v>
+        <v>1.398788027884284</v>
       </c>
       <c r="S211" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO211" t="inlineStr">
@@ -31750,22 +32273,22 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>D100</t>
+          <t>D004</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>Haemophilus influenzae</t>
+          <t>COVID-19</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>流感嗜血杆菌</t>
+          <t>新型冠状病毒感染</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -31779,13 +32302,13 @@
         </is>
       </c>
       <c r="N212" t="n">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="O212" t="n">
-        <v>11</v>
+        <v>57</v>
       </c>
       <c r="R212" t="n">
-        <v>0.122116415132755</v>
+        <v>0.6327850602333667</v>
       </c>
       <c r="S212" t="inlineStr">
         <is>
@@ -31895,22 +32418,22 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>D105</t>
+          <t>D007</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>Shigellosis</t>
+          <t>Hepatitis A</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>志贺菌病</t>
+          <t>甲型肝炎</t>
         </is>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -31924,17 +32447,22 @@
         </is>
       </c>
       <c r="N213" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="O213" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="R213" t="n">
-        <v>0.2553343225503059</v>
+        <v>0.08881193827836725</v>
       </c>
       <c r="S213" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO213" t="inlineStr">
@@ -32040,22 +32568,22 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>D106</t>
+          <t>D011</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>Invasive pneumococcal disease</t>
+          <t>Hepatitis E</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>侵袭性肺炎球菌病</t>
+          <t>戊型肝炎</t>
         </is>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -32069,17 +32597,22 @@
         </is>
       </c>
       <c r="N214" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="O214" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="R214" t="n">
-        <v>0.2553343225503059</v>
+        <v>0.07771044599357135</v>
       </c>
       <c r="S214" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO214" t="inlineStr">
@@ -32185,22 +32718,22 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>D108</t>
+          <t>D017</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t>Listeriosis</t>
+          <t>Measles</t>
         </is>
       </c>
       <c r="J215" t="inlineStr">
         <is>
-          <t>李斯特菌病</t>
+          <t>麻疹</t>
         </is>
       </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
@@ -32214,13 +32747,13 @@
         </is>
       </c>
       <c r="N215" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="O215" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="R215" t="n">
-        <v>0.1110149228479591</v>
+        <v>0</v>
       </c>
       <c r="S215" t="inlineStr">
         <is>
@@ -32330,22 +32863,22 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>D109</t>
+          <t>D021</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>Lyme disease</t>
+          <t>Dengue</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>莱姆病</t>
+          <t>登革热</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -32359,13 +32892,13 @@
         </is>
       </c>
       <c r="N216" t="n">
-        <v>1737</v>
+        <v>22</v>
       </c>
       <c r="O216" t="n">
-        <v>1737</v>
+        <v>22</v>
       </c>
       <c r="R216" t="n">
-        <v>19.28329209869049</v>
+        <v>0.2442328302655099</v>
       </c>
       <c r="S216" t="inlineStr">
         <is>
@@ -32475,17 +33008,17 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>D113</t>
+          <t>D025</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>Q fever</t>
+          <t>Tuberculosis</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>Q热</t>
+          <t>肺结核</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -32504,13 +33037,13 @@
         </is>
       </c>
       <c r="N217" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="O217" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="R217" t="n">
-        <v>0.1110149228479591</v>
+        <v>0.4218567068222445</v>
       </c>
       <c r="S217" t="inlineStr">
         <is>
@@ -32620,22 +33153,22 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>D114</t>
+          <t>D037</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Salmonellosis</t>
+          <t>Malaria</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>沙门氏菌病</t>
+          <t>疟疾</t>
         </is>
       </c>
       <c r="K218" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Parasitic</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
@@ -32649,13 +33182,13 @@
         </is>
       </c>
       <c r="N218" t="n">
-        <v>290</v>
+        <v>32</v>
       </c>
       <c r="O218" t="n">
-        <v>290</v>
+        <v>32</v>
       </c>
       <c r="R218" t="n">
-        <v>3.219432762590813</v>
+        <v>0.355247753113469</v>
       </c>
       <c r="S218" t="inlineStr">
         <is>
@@ -32765,22 +33298,22 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>D115</t>
+          <t>D038</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>Shiga toxin-producing Escherichia coli infection</t>
+          <t>Influenza</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>产志贺毒素大肠杆菌感染</t>
+          <t>流行性感冒</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
@@ -32794,13 +33327,13 @@
         </is>
       </c>
       <c r="N219" t="n">
-        <v>267</v>
+        <v>38</v>
       </c>
       <c r="O219" t="n">
-        <v>267</v>
+        <v>38</v>
       </c>
       <c r="R219" t="n">
-        <v>2.964098440040507</v>
+        <v>0.4218567068222445</v>
       </c>
       <c r="S219" t="inlineStr">
         <is>
@@ -32910,22 +33443,22 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>D123</t>
+          <t>D052</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>Tularemia</t>
+          <t>Chikungunya</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>土拉菌病</t>
+          <t>基孔肯雅热</t>
         </is>
       </c>
       <c r="K220" t="inlineStr">
         <is>
-          <t>Bacterial</t>
+          <t>Viral</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
@@ -32939,13 +33472,13 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="O220" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="R220" t="n">
-        <v>0.2553343225503059</v>
+        <v>0.03330447685438772</v>
       </c>
       <c r="S220" t="inlineStr">
         <is>
@@ -33055,22 +33588,22 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>D205</t>
+          <t>D092</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>Tick-borne encephalitis</t>
+          <t>Campylobacteriosis</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>蜱传脑炎</t>
+          <t>弯曲杆菌病</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
@@ -33084,17 +33617,22 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>103</v>
+        <v>1280</v>
       </c>
       <c r="O221" t="n">
-        <v>103</v>
+        <v>1280</v>
       </c>
       <c r="R221" t="n">
-        <v>1.143453705333978</v>
+        <v>14.20991012453876</v>
       </c>
       <c r="S221" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO221" t="inlineStr">
@@ -33200,42 +33738,42 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>D004</t>
+          <t>D100</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>COVID-19</t>
+          <t>Haemophilus influenzae</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>新型冠状病毒感染</t>
+          <t>流感嗜血杆菌</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N222" t="n">
-        <v>114</v>
+        <v>11</v>
       </c>
       <c r="O222" t="n">
-        <v>114</v>
+        <v>11</v>
       </c>
       <c r="R222" t="n">
-        <v>1.265570120466733</v>
+        <v>0.122116415132755</v>
       </c>
       <c r="S222" t="inlineStr">
         <is>
@@ -33345,46 +33883,51 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>D007</t>
+          <t>D105</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>Hepatitis A</t>
+          <t>Shigellosis</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>甲型肝炎</t>
+          <t>志贺菌病</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N223" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="O223" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="R223" t="n">
-        <v>0.1110149228479591</v>
+        <v>0.2553343225503059</v>
       </c>
       <c r="S223" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO223" t="inlineStr">
@@ -33490,42 +34033,42 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>D011</t>
+          <t>D106</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Hepatitis E</t>
+          <t>Invasive pneumococcal disease</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>戊型肝炎</t>
+          <t>侵袭性肺炎球菌病</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N224" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="O224" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="R224" t="n">
-        <v>0.08881193827836725</v>
+        <v>0.2553343225503059</v>
       </c>
       <c r="S224" t="inlineStr">
         <is>
@@ -33635,42 +34178,42 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>D038</t>
+          <t>D107</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>Influenza</t>
+          <t>Legionellosis</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>流行性感冒</t>
+          <t>军团菌病</t>
         </is>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t>Viral</t>
+          <t>Bacterial</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N225" t="n">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="O225" t="n">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="R225" t="n">
-        <v>1.432092504738672</v>
+        <v>1.065743259340407</v>
       </c>
       <c r="S225" t="inlineStr">
         <is>
@@ -33780,17 +34323,17 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>D092</t>
+          <t>D108</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Campylobacteriosis</t>
+          <t>Listeriosis</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>弯曲杆菌病</t>
+          <t>李斯特菌病</t>
         </is>
       </c>
       <c r="K226" t="inlineStr">
@@ -33800,22 +34343,22 @@
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N226" t="n">
-        <v>1392</v>
+        <v>10</v>
       </c>
       <c r="O226" t="n">
-        <v>1392</v>
+        <v>10</v>
       </c>
       <c r="R226" t="n">
-        <v>15.4532772604359</v>
+        <v>0.1110149228479591</v>
       </c>
       <c r="S226" t="inlineStr">
         <is>
@@ -33925,17 +34468,17 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>D105</t>
+          <t>D109</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>Shigellosis</t>
+          <t>Lyme disease</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>志贺菌病</t>
+          <t>莱姆病</t>
         </is>
       </c>
       <c r="K227" t="inlineStr">
@@ -33945,26 +34488,31 @@
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N227" t="n">
-        <v>27</v>
+        <v>1751</v>
       </c>
       <c r="O227" t="n">
-        <v>27</v>
+        <v>1751</v>
       </c>
       <c r="R227" t="n">
-        <v>0.2997402916894895</v>
+        <v>19.43871299067763</v>
       </c>
       <c r="S227" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO227" t="inlineStr">
@@ -34070,17 +34618,17 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>D109</t>
+          <t>D113</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Lyme disease</t>
+          <t>Q fever</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>莱姆病</t>
+          <t>Q热</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -34090,22 +34638,22 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N228" t="n">
-        <v>1129</v>
+        <v>11</v>
       </c>
       <c r="O228" t="n">
-        <v>1129</v>
+        <v>11</v>
       </c>
       <c r="R228" t="n">
-        <v>12.53358478953458</v>
+        <v>0.122116415132755</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
@@ -34235,26 +34783,31 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N229" t="n">
-        <v>555</v>
+        <v>290</v>
       </c>
       <c r="O229" t="n">
-        <v>555</v>
+        <v>290</v>
       </c>
       <c r="R229" t="n">
-        <v>6.161328218061729</v>
+        <v>3.219432762590813</v>
       </c>
       <c r="S229" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO229" t="inlineStr">
@@ -34380,26 +34933,31 @@
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N230" t="n">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="O230" t="n">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="R230" t="n">
-        <v>2.897489486331732</v>
+        <v>2.964098440040507</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO230" t="inlineStr">
@@ -34525,26 +35083,31 @@
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N231" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="O231" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="R231" t="n">
-        <v>0.08881193827836725</v>
+        <v>0.2553343225503059</v>
       </c>
       <c r="S231" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO231" t="inlineStr">
@@ -34670,26 +35233,31 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N232" t="n">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="O232" t="n">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="R232" t="n">
-        <v>0.2775373071198977</v>
+        <v>1.143453705333978</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO232" t="inlineStr">
@@ -34752,6 +35320,2516 @@
         </is>
       </c>
       <c r="BC232" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>D004</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr">
+        <is>
+          <t>COVID-19</t>
+        </is>
+      </c>
+      <c r="J233" t="inlineStr">
+        <is>
+          <t>新型冠状病毒感染</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L233" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M233" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N233" t="n">
+        <v>114</v>
+      </c>
+      <c r="O233" t="n">
+        <v>114</v>
+      </c>
+      <c r="R233" t="n">
+        <v>1.265570120466733</v>
+      </c>
+      <c r="S233" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO233" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP233" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR233" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS233" t="inlineStr"/>
+      <c r="AT233" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU233" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV233" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW233" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX233" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY233" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA233" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB233" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC233" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>D007</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr">
+        <is>
+          <t>Hepatitis A</t>
+        </is>
+      </c>
+      <c r="J234" t="inlineStr">
+        <is>
+          <t>甲型肝炎</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L234" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M234" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N234" t="n">
+        <v>10</v>
+      </c>
+      <c r="O234" t="n">
+        <v>10</v>
+      </c>
+      <c r="R234" t="n">
+        <v>0.1110149228479591</v>
+      </c>
+      <c r="S234" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO234" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP234" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR234" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS234" t="inlineStr"/>
+      <c r="AT234" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU234" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV234" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW234" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX234" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY234" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA234" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB234" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC234" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J235" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L235" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N235" t="n">
+        <v>8</v>
+      </c>
+      <c r="O235" t="n">
+        <v>8</v>
+      </c>
+      <c r="R235" t="n">
+        <v>0.08881193827836725</v>
+      </c>
+      <c r="S235" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO235" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP235" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR235" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS235" t="inlineStr"/>
+      <c r="AT235" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU235" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV235" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW235" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX235" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY235" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA235" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB235" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC235" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>D017</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr">
+        <is>
+          <t>Measles</t>
+        </is>
+      </c>
+      <c r="J236" t="inlineStr">
+        <is>
+          <t>麻疹</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L236" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M236" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N236" t="n">
+        <v>2</v>
+      </c>
+      <c r="O236" t="n">
+        <v>2</v>
+      </c>
+      <c r="R236" t="n">
+        <v>0.02220298456959181</v>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO236" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP236" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR236" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS236" t="inlineStr"/>
+      <c r="AT236" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU236" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV236" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW236" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX236" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY236" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA236" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB236" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC236" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>D037</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr">
+        <is>
+          <t>Malaria</t>
+        </is>
+      </c>
+      <c r="J237" t="inlineStr">
+        <is>
+          <t>疟疾</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Parasitic</t>
+        </is>
+      </c>
+      <c r="L237" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M237" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N237" t="n">
+        <v>31</v>
+      </c>
+      <c r="O237" t="n">
+        <v>31</v>
+      </c>
+      <c r="R237" t="n">
+        <v>0.3441462608286731</v>
+      </c>
+      <c r="S237" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO237" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP237" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR237" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS237" t="inlineStr"/>
+      <c r="AT237" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU237" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV237" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW237" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX237" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY237" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA237" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB237" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC237" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>D038</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr">
+        <is>
+          <t>Influenza</t>
+        </is>
+      </c>
+      <c r="J238" t="inlineStr">
+        <is>
+          <t>流行性感冒</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L238" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M238" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N238" t="n">
+        <v>130</v>
+      </c>
+      <c r="O238" t="n">
+        <v>130</v>
+      </c>
+      <c r="R238" t="n">
+        <v>1.443193997023468</v>
+      </c>
+      <c r="S238" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO238" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP238" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR238" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS238" t="inlineStr"/>
+      <c r="AT238" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU238" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV238" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW238" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX238" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY238" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA238" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB238" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC238" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>D092</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr">
+        <is>
+          <t>Campylobacteriosis</t>
+        </is>
+      </c>
+      <c r="J239" t="inlineStr">
+        <is>
+          <t>弯曲杆菌病</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L239" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M239" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N239" t="n">
+        <v>1392</v>
+      </c>
+      <c r="O239" t="n">
+        <v>1392</v>
+      </c>
+      <c r="R239" t="n">
+        <v>15.4532772604359</v>
+      </c>
+      <c r="S239" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO239" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP239" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR239" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS239" t="inlineStr"/>
+      <c r="AT239" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU239" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV239" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW239" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX239" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY239" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA239" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB239" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC239" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>D100</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Haemophilus influenzae</t>
+        </is>
+      </c>
+      <c r="J240" t="inlineStr">
+        <is>
+          <t>流感嗜血杆菌</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L240" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M240" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N240" t="n">
+        <v>10</v>
+      </c>
+      <c r="O240" t="n">
+        <v>10</v>
+      </c>
+      <c r="R240" t="n">
+        <v>0.1110149228479591</v>
+      </c>
+      <c r="S240" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO240" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP240" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR240" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS240" t="inlineStr"/>
+      <c r="AT240" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU240" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV240" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW240" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX240" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY240" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA240" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB240" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC240" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>D105</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr">
+        <is>
+          <t>Shigellosis</t>
+        </is>
+      </c>
+      <c r="J241" t="inlineStr">
+        <is>
+          <t>志贺菌病</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N241" t="n">
+        <v>27</v>
+      </c>
+      <c r="O241" t="n">
+        <v>27</v>
+      </c>
+      <c r="R241" t="n">
+        <v>0.2997402916894895</v>
+      </c>
+      <c r="S241" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO241" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP241" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR241" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS241" t="inlineStr"/>
+      <c r="AT241" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU241" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV241" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW241" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX241" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY241" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA241" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB241" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC241" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>D106</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Invasive pneumococcal disease</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>侵袭性肺炎球菌病</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L242" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N242" t="n">
+        <v>30</v>
+      </c>
+      <c r="O242" t="n">
+        <v>30</v>
+      </c>
+      <c r="R242" t="n">
+        <v>0.3330447685438772</v>
+      </c>
+      <c r="S242" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO242" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP242" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR242" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS242" t="inlineStr"/>
+      <c r="AT242" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU242" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV242" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW242" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX242" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY242" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA242" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB242" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC242" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>D108</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr">
+        <is>
+          <t>Listeriosis</t>
+        </is>
+      </c>
+      <c r="J243" t="inlineStr">
+        <is>
+          <t>李斯特菌病</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L243" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M243" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N243" t="n">
+        <v>5</v>
+      </c>
+      <c r="O243" t="n">
+        <v>5</v>
+      </c>
+      <c r="R243" t="n">
+        <v>0.05550746142397953</v>
+      </c>
+      <c r="S243" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO243" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP243" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR243" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS243" t="inlineStr"/>
+      <c r="AT243" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU243" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV243" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW243" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX243" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY243" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA243" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB243" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC243" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J244" t="inlineStr">
+        <is>
+          <t>莱姆病</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L244" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M244" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N244" t="n">
+        <v>1138</v>
+      </c>
+      <c r="O244" t="n">
+        <v>1138</v>
+      </c>
+      <c r="R244" t="n">
+        <v>12.63349822009774</v>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO244" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP244" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR244" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS244" t="inlineStr"/>
+      <c r="AT244" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU244" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV244" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW244" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX244" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY244" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA244" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB244" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC244" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>D113</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr">
+        <is>
+          <t>Q fever</t>
+        </is>
+      </c>
+      <c r="J245" t="inlineStr">
+        <is>
+          <t>Q热</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L245" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M245" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N245" t="n">
+        <v>11</v>
+      </c>
+      <c r="O245" t="n">
+        <v>11</v>
+      </c>
+      <c r="R245" t="n">
+        <v>0.122116415132755</v>
+      </c>
+      <c r="S245" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO245" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP245" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR245" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS245" t="inlineStr"/>
+      <c r="AT245" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU245" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV245" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW245" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX245" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY245" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA245" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB245" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC245" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>D114</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr">
+        <is>
+          <t>Salmonellosis</t>
+        </is>
+      </c>
+      <c r="J246" t="inlineStr">
+        <is>
+          <t>沙门氏菌病</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N246" t="n">
+        <v>555</v>
+      </c>
+      <c r="O246" t="n">
+        <v>555</v>
+      </c>
+      <c r="R246" t="n">
+        <v>6.161328218061729</v>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO246" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP246" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR246" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS246" t="inlineStr"/>
+      <c r="AT246" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU246" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV246" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW246" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX246" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY246" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA246" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB246" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC246" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>D115</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Shiga toxin-producing Escherichia coli infection</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>产志贺毒素大肠杆菌感染</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L247" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M247" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N247" t="n">
+        <v>261</v>
+      </c>
+      <c r="O247" t="n">
+        <v>261</v>
+      </c>
+      <c r="R247" t="n">
+        <v>2.897489486331732</v>
+      </c>
+      <c r="S247" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO247" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP247" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR247" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS247" t="inlineStr"/>
+      <c r="AT247" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU247" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV247" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW247" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX247" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY247" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA247" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB247" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC247" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>D123</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr">
+        <is>
+          <t>Tularemia</t>
+        </is>
+      </c>
+      <c r="J248" t="inlineStr">
+        <is>
+          <t>土拉菌病</t>
+        </is>
+      </c>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L248" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M248" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N248" t="n">
+        <v>8</v>
+      </c>
+      <c r="O248" t="n">
+        <v>8</v>
+      </c>
+      <c r="R248" t="n">
+        <v>0.08881193827836725</v>
+      </c>
+      <c r="S248" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO248" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP248" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR248" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS248" t="inlineStr"/>
+      <c r="AT248" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU248" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV248" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW248" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX248" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY248" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA248" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB248" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC248" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>D205</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr">
+        <is>
+          <t>Tick-borne encephalitis</t>
+        </is>
+      </c>
+      <c r="J249" t="inlineStr">
+        <is>
+          <t>蜱传脑炎</t>
+        </is>
+      </c>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L249" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M249" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N249" t="n">
+        <v>25</v>
+      </c>
+      <c r="O249" t="n">
+        <v>25</v>
+      </c>
+      <c r="R249" t="n">
+        <v>0.2775373071198977</v>
+      </c>
+      <c r="S249" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO249" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP249" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR249" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS249" t="inlineStr"/>
+      <c r="AT249" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU249" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV249" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW249" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX249" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY249" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA249" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB249" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC249" t="inlineStr">
         <is>
           <t>rest_api</t>
         </is>
@@ -34873,7 +37951,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>226</v>
+        <v>242</v>
       </c>
     </row>
     <row r="10">
@@ -34883,7 +37961,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>231</v>
+        <v>248</v>
       </c>
     </row>
     <row r="11">
@@ -34903,7 +37981,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
@@ -34935,7 +38013,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>58381</v>
+        <v>60765</v>
       </c>
     </row>
     <row r="16">

--- a/countries/ch/2026-2029.xlsx
+++ b/countries/ch/2026-2029.xlsx
@@ -768,11 +768,6 @@
       <c r="R2" t="n">
         <v>0.954728336492448</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -785,23 +780,13 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -915,17 +900,15 @@
       <c r="O3" t="n">
         <v>405</v>
       </c>
+      <c r="P3" t="n">
+        <v>405</v>
+      </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>4.496104375342342</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -938,23 +921,13 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -1068,17 +1041,15 @@
       <c r="O4" t="n">
         <v>2743</v>
       </c>
+      <c r="P4" t="n">
+        <v>2743</v>
+      </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>30.45139333719517</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1091,23 +1062,13 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -1221,17 +1182,15 @@
       <c r="O5" t="n">
         <v>298</v>
       </c>
+      <c r="P5" t="n">
+        <v>298</v>
+      </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>3.30824470086918</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1244,23 +1203,13 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -1374,17 +1323,15 @@
       <c r="O6" t="n">
         <v>2287</v>
       </c>
+      <c r="P6" t="n">
+        <v>2287</v>
+      </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>25.38911285532824</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1397,23 +1344,13 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -1527,17 +1464,15 @@
       <c r="O7" t="n">
         <v>248</v>
       </c>
+      <c r="P7" t="n">
+        <v>248</v>
+      </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>2.753170086629385</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1550,23 +1485,13 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -1680,17 +1605,15 @@
       <c r="O8" t="n">
         <v>1796</v>
       </c>
+      <c r="P8" t="n">
+        <v>1796</v>
+      </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>19.93828014349345</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1703,23 +1626,13 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -1833,17 +1746,15 @@
       <c r="O9" t="n">
         <v>240</v>
       </c>
+      <c r="P9" t="n">
+        <v>240</v>
+      </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>2.664358148351018</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1856,23 +1767,13 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV9" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -1986,17 +1887,15 @@
       <c r="O10" t="n">
         <v>1688</v>
       </c>
+      <c r="P10" t="n">
+        <v>1688</v>
+      </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>18.73931897673549</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2009,23 +1908,13 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV10" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -2142,11 +2031,6 @@
       <c r="R11" t="n">
         <v>1.454295489308264</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2159,23 +2043,13 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
       </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV11" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -2289,17 +2163,15 @@
       <c r="O12" t="n">
         <v>195</v>
       </c>
+      <c r="P12" t="n">
+        <v>195</v>
+      </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>2.164790995535202</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2312,23 +2184,13 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV12" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -2442,17 +2304,15 @@
       <c r="O13" t="n">
         <v>1232</v>
       </c>
+      <c r="P13" t="n">
+        <v>1232</v>
+      </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>13.67703849486856</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2465,23 +2325,13 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV13" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -2595,17 +2445,15 @@
       <c r="O14" t="n">
         <v>170</v>
       </c>
+      <c r="P14" t="n">
+        <v>170</v>
+      </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>1.887253688415304</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2618,23 +2466,13 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV14" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -2748,17 +2586,15 @@
       <c r="O15" t="n">
         <v>742</v>
       </c>
+      <c r="P15" t="n">
+        <v>742</v>
+      </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>8.237307275318562</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2771,23 +2607,13 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
       </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV15" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -2901,17 +2727,15 @@
       <c r="O16" t="n">
         <v>117</v>
       </c>
+      <c r="P16" t="n">
+        <v>117</v>
+      </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>1.298874597321121</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2924,23 +2748,13 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV16" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -3054,17 +2868,15 @@
       <c r="O17" t="n">
         <v>386</v>
       </c>
+      <c r="P17" t="n">
+        <v>386</v>
+      </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>4.285176021931219</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3077,23 +2889,13 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
       </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV17" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -3207,17 +3009,15 @@
       <c r="O18" t="n">
         <v>67</v>
       </c>
+      <c r="P18" t="n">
+        <v>67</v>
+      </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0.7437999830813258</v>
       </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3230,23 +3030,13 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
       </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV18" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -3360,17 +3150,15 @@
       <c r="O19" t="n">
         <v>238</v>
       </c>
+      <c r="P19" t="n">
+        <v>238</v>
+      </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>2.642155163781426</v>
       </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3383,23 +3171,13 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV19" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -3516,11 +3294,6 @@
       <c r="R20" t="n">
         <v>2.908590978616528</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3533,23 +3306,13 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV20" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -3663,17 +3426,15 @@
       <c r="O21" t="n">
         <v>68</v>
       </c>
+      <c r="P21" t="n">
+        <v>68</v>
+      </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0.7549014753661216</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3686,23 +3447,13 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV21" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -3816,17 +3567,15 @@
       <c r="O22" t="n">
         <v>130</v>
       </c>
+      <c r="P22" t="n">
+        <v>130</v>
+      </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>1.443193997023468</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3839,23 +3588,13 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV22" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -3969,14 +3708,12 @@
       <c r="O23" t="n">
         <v>44</v>
       </c>
+      <c r="P23" t="n">
+        <v>44</v>
+      </c>
       <c r="R23" t="n">
         <v>0.4884656605310199</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3989,23 +3726,13 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
       </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV23" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -4119,14 +3846,12 @@
       <c r="O24" t="n">
         <v>103</v>
       </c>
+      <c r="P24" t="n">
+        <v>103</v>
+      </c>
       <c r="R24" t="n">
         <v>1.143453705333978</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4139,23 +3864,13 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
       </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV24" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -4269,14 +3984,12 @@
       <c r="O25" t="n">
         <v>59</v>
       </c>
+      <c r="P25" t="n">
+        <v>59</v>
+      </c>
       <c r="R25" t="n">
         <v>0.6549880448029585</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4289,23 +4002,13 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
       </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV25" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -4419,14 +4122,12 @@
       <c r="O26" t="n">
         <v>67</v>
       </c>
+      <c r="P26" t="n">
+        <v>67</v>
+      </c>
       <c r="R26" t="n">
         <v>0.7437999830813258</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4439,23 +4140,13 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
       </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV26" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -4569,14 +4260,12 @@
       <c r="O27" t="n">
         <v>36</v>
       </c>
+      <c r="P27" t="n">
+        <v>36</v>
+      </c>
       <c r="R27" t="n">
         <v>0.3996537222526526</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4589,23 +4278,13 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
       </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV27" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -4719,14 +4398,12 @@
       <c r="O28" t="n">
         <v>50</v>
       </c>
+      <c r="P28" t="n">
+        <v>50</v>
+      </c>
       <c r="R28" t="n">
         <v>0.5550746142397954</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4739,23 +4416,13 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV28" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -4869,14 +4536,12 @@
       <c r="O29" t="n">
         <v>49</v>
       </c>
+      <c r="P29" t="n">
+        <v>49</v>
+      </c>
       <c r="R29" t="n">
         <v>0.5439731219549995</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4889,23 +4554,13 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
       </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV29" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -5019,14 +4674,12 @@
       <c r="O30" t="n">
         <v>52</v>
       </c>
+      <c r="P30" t="n">
+        <v>52</v>
+      </c>
       <c r="R30" t="n">
         <v>0.5772775988093871</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5039,23 +4692,13 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
       </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV30" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -5172,11 +4815,6 @@
       <c r="R31" t="n">
         <v>4.373987960209587</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5189,23 +4827,13 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV31" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -5319,14 +4947,12 @@
       <c r="O32" t="n">
         <v>27</v>
       </c>
+      <c r="P32" t="n">
+        <v>27</v>
+      </c>
       <c r="R32" t="n">
         <v>0.2997402916894895</v>
       </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5339,23 +4965,13 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR32" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
       </c>
-      <c r="AU32" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV32" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -5469,14 +5085,12 @@
       <c r="O33" t="n">
         <v>27</v>
       </c>
+      <c r="P33" t="n">
+        <v>27</v>
+      </c>
       <c r="R33" t="n">
         <v>0.2997402916894895</v>
       </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5489,23 +5103,13 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR33" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
       </c>
-      <c r="AU33" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV33" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -5619,14 +5223,12 @@
       <c r="O34" t="n">
         <v>25</v>
       </c>
+      <c r="P34" t="n">
+        <v>25</v>
+      </c>
       <c r="R34" t="n">
         <v>0.2775373071198977</v>
       </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5639,23 +5241,13 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR34" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
-      <c r="AU34" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV34" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -5769,14 +5361,12 @@
       <c r="O35" t="n">
         <v>22</v>
       </c>
+      <c r="P35" t="n">
+        <v>22</v>
+      </c>
       <c r="R35" t="n">
         <v>0.2442328302655099</v>
       </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5789,23 +5379,13 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR35" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
       </c>
-      <c r="AU35" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV35" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -5919,14 +5499,12 @@
       <c r="O36" t="n">
         <v>9</v>
       </c>
+      <c r="P36" t="n">
+        <v>9</v>
+      </c>
       <c r="R36" t="n">
         <v>0.09991343056316315</v>
       </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5939,23 +5517,13 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR36" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
       </c>
-      <c r="AU36" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV36" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -6069,14 +5637,12 @@
       <c r="O37" t="n">
         <v>14</v>
       </c>
+      <c r="P37" t="n">
+        <v>14</v>
+      </c>
       <c r="R37" t="n">
         <v>0.1554208919871427</v>
       </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6089,23 +5655,13 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
       </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV37" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -6219,14 +5775,12 @@
       <c r="O38" t="n">
         <v>11</v>
       </c>
+      <c r="P38" t="n">
+        <v>11</v>
+      </c>
       <c r="R38" t="n">
         <v>0.122116415132755</v>
       </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6239,23 +5793,13 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR38" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
       </c>
-      <c r="AU38" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV38" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -6369,14 +5913,12 @@
       <c r="O39" t="n">
         <v>8</v>
       </c>
+      <c r="P39" t="n">
+        <v>8</v>
+      </c>
       <c r="R39" t="n">
         <v>0.08881193827836725</v>
       </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6389,23 +5931,13 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
       </c>
-      <c r="AU39" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV39" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -6522,11 +6054,6 @@
       <c r="R40" t="n">
         <v>9.724907241481215</v>
       </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6539,23 +6066,13 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
       </c>
-      <c r="AU40" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV40" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -6669,14 +6186,12 @@
       <c r="O41" t="n">
         <v>14</v>
       </c>
+      <c r="P41" t="n">
+        <v>14</v>
+      </c>
       <c r="R41" t="n">
         <v>0.1554208919871427</v>
       </c>
-      <c r="S41" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6689,23 +6204,13 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR41" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
       </c>
-      <c r="AU41" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV41" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -6819,14 +6324,12 @@
       <c r="O42" t="n">
         <v>11</v>
       </c>
+      <c r="P42" t="n">
+        <v>11</v>
+      </c>
       <c r="R42" t="n">
         <v>0.122116415132755</v>
       </c>
-      <c r="S42" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6839,23 +6342,13 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR42" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
       </c>
-      <c r="AU42" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV42" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -6969,14 +6462,12 @@
       <c r="O43" t="n">
         <v>12</v>
       </c>
+      <c r="P43" t="n">
+        <v>12</v>
+      </c>
       <c r="R43" t="n">
         <v>0.1332179074175509</v>
       </c>
-      <c r="S43" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6989,23 +6480,13 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR43" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
       </c>
-      <c r="AU43" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV43" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -7119,14 +6600,12 @@
       <c r="O44" t="n">
         <v>10</v>
       </c>
+      <c r="P44" t="n">
+        <v>10</v>
+      </c>
       <c r="R44" t="n">
         <v>0.1110149228479591</v>
       </c>
-      <c r="S44" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7139,23 +6618,13 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR44" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
       </c>
-      <c r="AU44" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV44" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -7269,14 +6738,12 @@
       <c r="O45" t="n">
         <v>17</v>
       </c>
+      <c r="P45" t="n">
+        <v>17</v>
+      </c>
       <c r="R45" t="n">
         <v>0.1887253688415304</v>
       </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7289,23 +6756,13 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR45" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
       </c>
-      <c r="AU45" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV45" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -7419,14 +6876,12 @@
       <c r="O46" t="n">
         <v>11</v>
       </c>
+      <c r="P46" t="n">
+        <v>11</v>
+      </c>
       <c r="R46" t="n">
         <v>0.122116415132755</v>
       </c>
-      <c r="S46" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7439,23 +6894,13 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR46" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
       </c>
-      <c r="AU46" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV46" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -7569,14 +7014,12 @@
       <c r="O47" t="n">
         <v>7</v>
       </c>
+      <c r="P47" t="n">
+        <v>7</v>
+      </c>
       <c r="R47" t="n">
         <v>0.07771044599357135</v>
       </c>
-      <c r="S47" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7589,23 +7032,13 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR47" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
       </c>
-      <c r="AU47" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV47" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -7719,14 +7152,12 @@
       <c r="O48" t="n">
         <v>7</v>
       </c>
+      <c r="P48" t="n">
+        <v>7</v>
+      </c>
       <c r="R48" t="n">
         <v>0.07771044599357135</v>
       </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7739,23 +7170,13 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR48" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
       </c>
-      <c r="AU48" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV48" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -7872,11 +7293,6 @@
       <c r="R49" t="n">
         <v>24.30116661141824</v>
       </c>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7889,23 +7305,13 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR49" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
       </c>
-      <c r="AU49" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV49" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -8022,11 +7428,6 @@
       <c r="R50" t="n">
         <v>19.43871299067763</v>
       </c>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8039,23 +7440,13 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR50" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
       </c>
-      <c r="AU50" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV50" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -8172,11 +7563,6 @@
       <c r="R51" t="n">
         <v>12.63349822009774</v>
       </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -8189,22 +7575,12 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR51" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
-      </c>
-      <c r="AU51" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV51" t="inlineStr">
         <is>

--- a/countries/ch/2026-2029.xlsx
+++ b/countries/ch/2026-2029.xlsx
@@ -4807,13 +4807,13 @@
         </is>
       </c>
       <c r="N31" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="O31" t="n">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="R31" t="n">
-        <v>4.373987960209587</v>
+        <v>4.396190944779179</v>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
@@ -6046,13 +6046,13 @@
         </is>
       </c>
       <c r="N40" t="n">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="O40" t="n">
-        <v>876</v>
+        <v>879</v>
       </c>
       <c r="R40" t="n">
-        <v>9.724907241481215</v>
+        <v>9.758211718335602</v>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
@@ -7285,13 +7285,13 @@
         </is>
       </c>
       <c r="N49" t="n">
-        <v>2189</v>
+        <v>2200</v>
       </c>
       <c r="O49" t="n">
-        <v>2189</v>
+        <v>2200</v>
       </c>
       <c r="R49" t="n">
-        <v>24.30116661141824</v>
+        <v>24.42328302655099</v>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
@@ -7420,13 +7420,13 @@
         </is>
       </c>
       <c r="N50" t="n">
-        <v>1751</v>
+        <v>1759</v>
       </c>
       <c r="O50" t="n">
-        <v>1751</v>
+        <v>1759</v>
       </c>
       <c r="R50" t="n">
-        <v>19.43871299067763</v>
+        <v>19.527524928956</v>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
@@ -7555,13 +7555,13 @@
         </is>
       </c>
       <c r="N51" t="n">
-        <v>1138</v>
+        <v>1144</v>
       </c>
       <c r="O51" t="n">
-        <v>1138</v>
+        <v>1144</v>
       </c>
       <c r="R51" t="n">
-        <v>12.63349822009774</v>
+        <v>12.70010717380652</v>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
@@ -7618,6 +7618,141 @@
         </is>
       </c>
       <c r="BC51" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ch</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Switzerland</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>D109</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Lyme disease</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>莱姆病</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>616</v>
+      </c>
+      <c r="O52" t="n">
+        <v>616</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6.838519247434278</v>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>rest_api</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>foph_idd</t>
+        </is>
+      </c>
+      <c r="BA52" t="inlineStr">
+        <is>
+          <t>Switzerland FOPH IDD</t>
+        </is>
+      </c>
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
+        </is>
+      </c>
+      <c r="BC52" t="inlineStr">
         <is>
           <t>rest_api</t>
         </is>
@@ -7656,7 +7791,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-09-01</t>
         </is>
       </c>
     </row>
@@ -7739,7 +7874,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10">
@@ -7749,7 +7884,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11">
@@ -7801,7 +7936,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20569</v>
+        <v>21215</v>
       </c>
     </row>
     <row r="16">

--- a/countries/ch/2026-2029.xlsx
+++ b/countries/ch/2026-2029.xlsx
@@ -768,6 +768,11 @@
       <c r="R2" t="n">
         <v>0.954728336492448</v>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -780,13 +785,23 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -900,15 +915,17 @@
       <c r="O3" t="n">
         <v>405</v>
       </c>
-      <c r="P3" t="n">
-        <v>405</v>
-      </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>4.496104375342342</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -921,13 +938,23 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -1041,15 +1068,17 @@
       <c r="O4" t="n">
         <v>2743</v>
       </c>
-      <c r="P4" t="n">
-        <v>2743</v>
-      </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>30.45139333719517</v>
       </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1062,13 +1091,23 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -1182,15 +1221,17 @@
       <c r="O5" t="n">
         <v>298</v>
       </c>
-      <c r="P5" t="n">
-        <v>298</v>
-      </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>3.30824470086918</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1203,13 +1244,23 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -1323,15 +1374,17 @@
       <c r="O6" t="n">
         <v>2287</v>
       </c>
-      <c r="P6" t="n">
-        <v>2287</v>
-      </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>25.38911285532824</v>
       </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1344,13 +1397,23 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -1464,15 +1527,17 @@
       <c r="O7" t="n">
         <v>248</v>
       </c>
-      <c r="P7" t="n">
-        <v>248</v>
-      </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>2.753170086629385</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1485,13 +1550,23 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -1605,15 +1680,17 @@
       <c r="O8" t="n">
         <v>1796</v>
       </c>
-      <c r="P8" t="n">
-        <v>1796</v>
-      </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>19.93828014349345</v>
       </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1626,13 +1703,23 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -1746,15 +1833,17 @@
       <c r="O9" t="n">
         <v>240</v>
       </c>
-      <c r="P9" t="n">
-        <v>240</v>
-      </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>2.664358148351018</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1767,13 +1856,23 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV9" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -1887,15 +1986,17 @@
       <c r="O10" t="n">
         <v>1688</v>
       </c>
-      <c r="P10" t="n">
-        <v>1688</v>
-      </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>18.73931897673549</v>
       </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -1908,13 +2009,23 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV10" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -2031,6 +2142,11 @@
       <c r="R11" t="n">
         <v>1.454295489308264</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2043,13 +2159,23 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
       </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV11" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -2163,15 +2289,17 @@
       <c r="O12" t="n">
         <v>195</v>
       </c>
-      <c r="P12" t="n">
-        <v>195</v>
-      </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>2.164790995535202</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2184,13 +2312,23 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV12" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -2304,15 +2442,17 @@
       <c r="O13" t="n">
         <v>1232</v>
       </c>
-      <c r="P13" t="n">
-        <v>1232</v>
-      </c>
       <c r="Q13" t="n">
         <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>13.67703849486856</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2325,13 +2465,23 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV13" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -2445,15 +2595,17 @@
       <c r="O14" t="n">
         <v>170</v>
       </c>
-      <c r="P14" t="n">
-        <v>170</v>
-      </c>
       <c r="Q14" t="n">
         <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>1.887253688415304</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2466,13 +2618,23 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV14" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -2586,15 +2748,17 @@
       <c r="O15" t="n">
         <v>742</v>
       </c>
-      <c r="P15" t="n">
-        <v>742</v>
-      </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>8.237307275318562</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2607,13 +2771,23 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
       </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV15" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -2727,15 +2901,17 @@
       <c r="O16" t="n">
         <v>117</v>
       </c>
-      <c r="P16" t="n">
-        <v>117</v>
-      </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>1.298874597321121</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2748,13 +2924,23 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
       </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV16" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -2868,15 +3054,17 @@
       <c r="O17" t="n">
         <v>386</v>
       </c>
-      <c r="P17" t="n">
-        <v>386</v>
-      </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>4.285176021931219</v>
       </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -2889,13 +3077,23 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
       </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV17" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -3009,15 +3207,17 @@
       <c r="O18" t="n">
         <v>67</v>
       </c>
-      <c r="P18" t="n">
-        <v>67</v>
-      </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0.7437999830813258</v>
       </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3030,13 +3230,23 @@
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="n">
         <v>0</v>
       </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV18" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -3150,15 +3360,17 @@
       <c r="O19" t="n">
         <v>238</v>
       </c>
-      <c r="P19" t="n">
-        <v>238</v>
-      </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>2.642155163781426</v>
       </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3171,13 +3383,23 @@
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="n">
         <v>0</v>
       </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV19" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -3294,6 +3516,11 @@
       <c r="R20" t="n">
         <v>2.908590978616528</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3306,13 +3533,23 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV20" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -3426,15 +3663,17 @@
       <c r="O21" t="n">
         <v>68</v>
       </c>
-      <c r="P21" t="n">
-        <v>68</v>
-      </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0.7549014753661216</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3447,13 +3686,23 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
       </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV21" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -3567,15 +3816,17 @@
       <c r="O22" t="n">
         <v>130</v>
       </c>
-      <c r="P22" t="n">
-        <v>130</v>
-      </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>1.443193997023468</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3588,13 +3839,23 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
       </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV22" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -3708,12 +3969,14 @@
       <c r="O23" t="n">
         <v>44</v>
       </c>
-      <c r="P23" t="n">
-        <v>44</v>
-      </c>
       <c r="R23" t="n">
         <v>0.4884656605310199</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3726,13 +3989,23 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
       </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV23" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -3846,12 +4119,14 @@
       <c r="O24" t="n">
         <v>103</v>
       </c>
-      <c r="P24" t="n">
-        <v>103</v>
-      </c>
       <c r="R24" t="n">
         <v>1.143453705333978</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -3864,13 +4139,23 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
       </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV24" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -3984,12 +4269,14 @@
       <c r="O25" t="n">
         <v>59</v>
       </c>
-      <c r="P25" t="n">
-        <v>59</v>
-      </c>
       <c r="R25" t="n">
         <v>0.6549880448029585</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4002,13 +4289,23 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
       </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV25" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -4122,12 +4419,14 @@
       <c r="O26" t="n">
         <v>67</v>
       </c>
-      <c r="P26" t="n">
-        <v>67</v>
-      </c>
       <c r="R26" t="n">
         <v>0.7437999830813258</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4140,13 +4439,23 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
       </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV26" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -4260,12 +4569,14 @@
       <c r="O27" t="n">
         <v>36</v>
       </c>
-      <c r="P27" t="n">
-        <v>36</v>
-      </c>
       <c r="R27" t="n">
         <v>0.3996537222526526</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4278,13 +4589,23 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
       </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV27" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -4398,12 +4719,14 @@
       <c r="O28" t="n">
         <v>50</v>
       </c>
-      <c r="P28" t="n">
-        <v>50</v>
-      </c>
       <c r="R28" t="n">
         <v>0.5550746142397954</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4416,13 +4739,23 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
       </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV28" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -4536,12 +4869,14 @@
       <c r="O29" t="n">
         <v>49</v>
       </c>
-      <c r="P29" t="n">
-        <v>49</v>
-      </c>
       <c r="R29" t="n">
         <v>0.5439731219549995</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4554,13 +4889,23 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
       </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV29" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -4674,12 +5019,14 @@
       <c r="O30" t="n">
         <v>52</v>
       </c>
-      <c r="P30" t="n">
-        <v>52</v>
-      </c>
       <c r="R30" t="n">
         <v>0.5772775988093871</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4692,13 +5039,23 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
       </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV30" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -4815,6 +5172,11 @@
       <c r="R31" t="n">
         <v>4.396190944779179</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4827,13 +5189,23 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
       </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV31" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -4947,12 +5319,14 @@
       <c r="O32" t="n">
         <v>27</v>
       </c>
-      <c r="P32" t="n">
-        <v>27</v>
-      </c>
       <c r="R32" t="n">
         <v>0.2997402916894895</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -4965,13 +5339,23 @@
       </c>
       <c r="AP32" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="n">
         <v>0</v>
       </c>
+      <c r="AU32" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV32" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -5085,12 +5469,14 @@
       <c r="O33" t="n">
         <v>27</v>
       </c>
-      <c r="P33" t="n">
-        <v>27</v>
-      </c>
       <c r="R33" t="n">
         <v>0.2997402916894895</v>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5103,13 +5489,23 @@
       </c>
       <c r="AP33" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR33" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="n">
         <v>0</v>
       </c>
+      <c r="AU33" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV33" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -5223,12 +5619,14 @@
       <c r="O34" t="n">
         <v>25</v>
       </c>
-      <c r="P34" t="n">
-        <v>25</v>
-      </c>
       <c r="R34" t="n">
         <v>0.2775373071198977</v>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5241,13 +5639,23 @@
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR34" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="n">
         <v>0</v>
       </c>
+      <c r="AU34" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV34" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -5361,12 +5769,14 @@
       <c r="O35" t="n">
         <v>22</v>
       </c>
-      <c r="P35" t="n">
-        <v>22</v>
-      </c>
       <c r="R35" t="n">
         <v>0.2442328302655099</v>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5379,13 +5789,23 @@
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR35" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="n">
         <v>0</v>
       </c>
+      <c r="AU35" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV35" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -5499,12 +5919,14 @@
       <c r="O36" t="n">
         <v>9</v>
       </c>
-      <c r="P36" t="n">
-        <v>9</v>
-      </c>
       <c r="R36" t="n">
         <v>0.09991343056316315</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5517,13 +5939,23 @@
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="n">
         <v>0</v>
       </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV36" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -5637,12 +6069,14 @@
       <c r="O37" t="n">
         <v>14</v>
       </c>
-      <c r="P37" t="n">
-        <v>14</v>
-      </c>
       <c r="R37" t="n">
         <v>0.1554208919871427</v>
       </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5655,13 +6089,23 @@
       </c>
       <c r="AP37" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="n">
         <v>0</v>
       </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV37" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -5775,12 +6219,14 @@
       <c r="O38" t="n">
         <v>11</v>
       </c>
-      <c r="P38" t="n">
-        <v>11</v>
-      </c>
       <c r="R38" t="n">
         <v>0.122116415132755</v>
       </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5793,13 +6239,23 @@
       </c>
       <c r="AP38" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="n">
         <v>0</v>
       </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV38" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -5913,12 +6369,14 @@
       <c r="O39" t="n">
         <v>8</v>
       </c>
-      <c r="P39" t="n">
-        <v>8</v>
-      </c>
       <c r="R39" t="n">
         <v>0.08881193827836725</v>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -5931,13 +6389,23 @@
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="n">
         <v>0</v>
       </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV39" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -6054,6 +6522,11 @@
       <c r="R40" t="n">
         <v>9.758211718335602</v>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -6066,13 +6539,23 @@
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="n">
         <v>0</v>
       </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV40" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -6186,12 +6669,14 @@
       <c r="O41" t="n">
         <v>14</v>
       </c>
-      <c r="P41" t="n">
-        <v>14</v>
-      </c>
       <c r="R41" t="n">
         <v>0.1554208919871427</v>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6204,13 +6689,23 @@
       </c>
       <c r="AP41" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="n">
         <v>0</v>
       </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV41" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -6324,12 +6819,14 @@
       <c r="O42" t="n">
         <v>11</v>
       </c>
-      <c r="P42" t="n">
-        <v>11</v>
-      </c>
       <c r="R42" t="n">
         <v>0.122116415132755</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6342,13 +6839,23 @@
       </c>
       <c r="AP42" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR42" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="n">
         <v>0</v>
       </c>
+      <c r="AU42" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV42" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -6462,12 +6969,14 @@
       <c r="O43" t="n">
         <v>12</v>
       </c>
-      <c r="P43" t="n">
-        <v>12</v>
-      </c>
       <c r="R43" t="n">
         <v>0.1332179074175509</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6480,13 +6989,23 @@
       </c>
       <c r="AP43" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR43" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="n">
         <v>0</v>
       </c>
+      <c r="AU43" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV43" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -6600,12 +7119,14 @@
       <c r="O44" t="n">
         <v>10</v>
       </c>
-      <c r="P44" t="n">
-        <v>10</v>
-      </c>
       <c r="R44" t="n">
         <v>0.1110149228479591</v>
       </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6618,13 +7139,23 @@
       </c>
       <c r="AP44" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR44" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="n">
         <v>0</v>
       </c>
+      <c r="AU44" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV44" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -6738,12 +7269,14 @@
       <c r="O45" t="n">
         <v>17</v>
       </c>
-      <c r="P45" t="n">
-        <v>17</v>
-      </c>
       <c r="R45" t="n">
         <v>0.1887253688415304</v>
       </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6756,13 +7289,23 @@
       </c>
       <c r="AP45" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR45" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="n">
         <v>0</v>
       </c>
+      <c r="AU45" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV45" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -6876,12 +7419,14 @@
       <c r="O46" t="n">
         <v>11</v>
       </c>
-      <c r="P46" t="n">
-        <v>11</v>
-      </c>
       <c r="R46" t="n">
         <v>0.122116415132755</v>
       </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -6894,13 +7439,23 @@
       </c>
       <c r="AP46" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR46" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="n">
         <v>0</v>
       </c>
+      <c r="AU46" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV46" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -7014,12 +7569,14 @@
       <c r="O47" t="n">
         <v>7</v>
       </c>
-      <c r="P47" t="n">
-        <v>7</v>
-      </c>
       <c r="R47" t="n">
         <v>0.07771044599357135</v>
       </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7032,13 +7589,23 @@
       </c>
       <c r="AP47" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR47" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="n">
         <v>0</v>
       </c>
+      <c r="AU47" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV47" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -7152,12 +7719,14 @@
       <c r="O48" t="n">
         <v>7</v>
       </c>
-      <c r="P48" t="n">
-        <v>7</v>
-      </c>
       <c r="R48" t="n">
         <v>0.07771044599357135</v>
       </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -7170,13 +7739,23 @@
       </c>
       <c r="AP48" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR48" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS48" t="inlineStr"/>
       <c r="AT48" t="n">
         <v>0</v>
       </c>
+      <c r="AU48" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV48" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -7293,6 +7872,11 @@
       <c r="R49" t="n">
         <v>24.42328302655099</v>
       </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7305,13 +7889,23 @@
       </c>
       <c r="AP49" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR49" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="n">
         <v>0</v>
       </c>
+      <c r="AU49" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV49" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -7428,6 +8022,11 @@
       <c r="R50" t="n">
         <v>19.527524928956</v>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7440,13 +8039,23 @@
       </c>
       <c r="AP50" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR50" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="n">
         <v>0</v>
       </c>
+      <c r="AU50" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV50" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -7563,6 +8172,11 @@
       <c r="R51" t="n">
         <v>12.70010717380652</v>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7575,13 +8189,23 @@
       </c>
       <c r="AP51" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR51" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="n">
         <v>0</v>
       </c>
+      <c r="AU51" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
       <c r="AV51" t="inlineStr">
         <is>
           <t>foph_idd</t>
@@ -7698,6 +8322,11 @@
       <c r="R52" t="n">
         <v>6.838519247434278</v>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -7710,12 +8339,22 @@
       </c>
       <c r="AP52" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="n">
         <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
